--- a/Практика/УП0.3/нормализациия 2.xlsx
+++ b/Практика/УП0.3/нормализациия 2.xlsx
@@ -109,7 +109,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,19 +128,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -333,64 +328,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,7 +702,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -717,837 +713,837 @@
   <dimension ref="A2:G62"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="15" thickBot="1"/>
     <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="19.5" customHeight="1"/>
     <row r="5" spans="1:7" ht="18.5" customHeight="1">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="B5" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.5">
-      <c r="A6" s="1">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6" spans="1:7">
+      <c r="A6" s="19">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19">
         <v>111</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="19">
         <v>10</v>
       </c>
-      <c r="E6" s="1">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="E6" s="19">
+        <v>3</v>
+      </c>
+      <c r="F6" s="19">
+        <v>3</v>
+      </c>
+      <c r="G6" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.5">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7" spans="1:7">
+      <c r="A7" s="19">
+        <v>2</v>
+      </c>
+      <c r="B7" s="19">
         <v>112</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="19">
         <v>10</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="19">
         <v>6</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="F7" s="19">
+        <v>1</v>
+      </c>
+      <c r="G7" s="19">
         <v>25000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.5">
-      <c r="A8" s="1">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8" spans="1:7">
+      <c r="A8" s="19">
+        <v>3</v>
+      </c>
+      <c r="B8" s="19">
         <v>113</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="19">
         <v>11</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="19">
         <v>12</v>
       </c>
-      <c r="F8" s="1">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="F8" s="19">
+        <v>4</v>
+      </c>
+      <c r="G8" s="19">
         <v>18000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.5">
-      <c r="A9" s="1">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9" spans="1:7">
+      <c r="A9" s="19">
+        <v>4</v>
+      </c>
+      <c r="B9" s="19">
         <v>114</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="19">
         <v>15</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="19">
         <v>8</v>
       </c>
-      <c r="F9" s="1">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F9" s="19">
+        <v>4</v>
+      </c>
+      <c r="G9" s="19">
         <v>17000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.5">
-      <c r="A10" s="1">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10" spans="1:7">
+      <c r="A10" s="19">
+        <v>1</v>
+      </c>
+      <c r="B10" s="19">
         <v>111</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="19">
         <v>15</v>
       </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="E10" s="19">
+        <v>2</v>
+      </c>
+      <c r="F10" s="19">
+        <v>3</v>
+      </c>
+      <c r="G10" s="19">
         <v>20000</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1"/>
     <row r="12" spans="1:7" ht="25" customHeight="1" thickBot="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="14" spans="1:7" ht="17.5" customHeight="1">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="15" t="s">
+      <c r="B14" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.5">
-      <c r="A15" s="1">
-        <v>1</v>
-      </c>
-      <c r="B15" s="1">
+    <row r="15" spans="1:7">
+      <c r="A15" s="19">
+        <v>1</v>
+      </c>
+      <c r="B15" s="19">
         <v>111</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="19">
         <v>10</v>
       </c>
-      <c r="E15" s="1">
-        <v>3</v>
-      </c>
-      <c r="F15" s="1">
-        <v>3</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="E15" s="19">
+        <v>3</v>
+      </c>
+      <c r="F15" s="19">
+        <v>3</v>
+      </c>
+      <c r="G15" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.5">
-      <c r="A16" s="1">
-        <v>2</v>
-      </c>
-      <c r="B16" s="1">
+    <row r="16" spans="1:7">
+      <c r="A16" s="19">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19">
         <v>112</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="19">
         <v>10</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="19">
         <v>6</v>
       </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="F16" s="19">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19">
         <v>25000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.5">
-      <c r="A17" s="1">
-        <v>3</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="17" spans="1:7">
+      <c r="A17" s="19">
+        <v>3</v>
+      </c>
+      <c r="B17" s="19">
         <v>113</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="19">
         <v>11</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="19">
         <v>12</v>
       </c>
-      <c r="F17" s="1">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="F17" s="19">
+        <v>4</v>
+      </c>
+      <c r="G17" s="19">
         <v>18000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.5">
-      <c r="A18" s="1">
-        <v>4</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="18" spans="1:7">
+      <c r="A18" s="19">
+        <v>4</v>
+      </c>
+      <c r="B18" s="19">
         <v>114</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="19">
         <v>15</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="19">
         <v>8</v>
       </c>
-      <c r="F18" s="1">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="F18" s="19">
+        <v>4</v>
+      </c>
+      <c r="G18" s="19">
         <v>17000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.5">
-      <c r="A19" s="1">
-        <v>1</v>
-      </c>
-      <c r="B19" s="1">
+    <row r="19" spans="1:7">
+      <c r="A19" s="19">
+        <v>1</v>
+      </c>
+      <c r="B19" s="19">
         <v>111</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="19">
         <v>15</v>
       </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1">
-        <v>3</v>
-      </c>
-      <c r="G19" s="1">
+      <c r="E19" s="19">
+        <v>2</v>
+      </c>
+      <c r="F19" s="19">
+        <v>3</v>
+      </c>
+      <c r="G19" s="19">
         <v>20000</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1"/>
     <row r="21" spans="1:7" ht="22" customHeight="1" thickBot="1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1"/>
     <row r="23" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
-    </row>
-    <row r="24" spans="1:7" ht="16.5">
-      <c r="A24" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="16" t="s">
+      <c r="C24" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.5">
-      <c r="A25" s="1">
+    <row r="25" spans="1:7">
+      <c r="A25" s="19">
         <v>111</v>
       </c>
-      <c r="B25" s="1">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="B25" s="19">
+        <v>1</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="1">
-        <v>3</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D25" s="19">
+        <v>3</v>
+      </c>
+      <c r="E25" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.5">
-      <c r="A26" s="1">
+    <row r="26" spans="1:7">
+      <c r="A26" s="19">
         <v>112</v>
       </c>
-      <c r="B26" s="1">
-        <v>2</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="B26" s="19">
+        <v>2</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="D26" s="19">
+        <v>1</v>
+      </c>
+      <c r="E26" s="19">
         <v>25000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.5">
-      <c r="A27" s="1">
+    <row r="27" spans="1:7">
+      <c r="A27" s="19">
         <v>113</v>
       </c>
-      <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="B27" s="19">
+        <v>3</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="1">
-        <v>4</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D27" s="19">
+        <v>4</v>
+      </c>
+      <c r="E27" s="19">
         <v>18000</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.5">
-      <c r="A28" s="1">
+    <row r="28" spans="1:7">
+      <c r="A28" s="19">
         <v>114</v>
       </c>
-      <c r="B28" s="1">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="B28" s="19">
+        <v>4</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="1">
-        <v>4</v>
-      </c>
-      <c r="E28" s="1">
+      <c r="D28" s="19">
+        <v>4</v>
+      </c>
+      <c r="E28" s="19">
         <v>17000</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1"/>
     <row r="30" spans="1:7" ht="15" thickBot="1">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
     </row>
     <row r="31" spans="1:7" ht="18.5" customHeight="1">
-      <c r="A31" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="A31" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.5">
-      <c r="A32" s="1">
+    <row r="32" spans="1:7">
+      <c r="A32" s="19">
         <v>111</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="19">
         <v>10</v>
       </c>
-      <c r="C32" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="16.5">
-      <c r="A33" s="1">
+      <c r="C32" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="19">
         <v>112</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="19">
         <v>10</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="19">
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.5">
-      <c r="A34" s="1">
+    <row r="34" spans="1:7">
+      <c r="A34" s="19">
         <v>113</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="19">
         <v>11</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="19">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.5">
-      <c r="A35" s="1">
+    <row r="35" spans="1:7">
+      <c r="A35" s="19">
         <v>114</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="19">
         <v>15</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="19">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.5">
-      <c r="A36" s="1">
+    <row r="36" spans="1:7">
+      <c r="A36" s="19">
         <v>111</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="19">
         <v>15</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1"/>
     <row r="38" spans="1:7" ht="27" customHeight="1" thickBot="1">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1"/>
     <row r="40" spans="1:7" ht="15" thickBot="1">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="19"/>
-      <c r="F40" s="10" t="s">
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15"/>
+      <c r="F40" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="13"/>
-    </row>
-    <row r="41" spans="1:7" ht="16.5">
-      <c r="A41" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="16" t="s">
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="16" t="s">
+      <c r="C41" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.5">
-      <c r="A42" s="1">
+    <row r="42" spans="1:7">
+      <c r="A42" s="19">
         <v>111</v>
       </c>
-      <c r="B42" s="1">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="B42" s="19">
+        <v>1</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="1">
-        <v>3</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1</v>
-      </c>
-      <c r="G42" s="1">
+      <c r="D42" s="19">
+        <v>3</v>
+      </c>
+      <c r="F42" s="19">
+        <v>1</v>
+      </c>
+      <c r="G42" s="19">
         <v>25000</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.5">
-      <c r="A43" s="1">
+    <row r="43" spans="1:7">
+      <c r="A43" s="19">
         <v>112</v>
       </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="B43" s="19">
+        <v>2</v>
+      </c>
+      <c r="C43" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="F43" s="1">
-        <v>3</v>
-      </c>
-      <c r="G43" s="1">
+      <c r="D43" s="19">
+        <v>1</v>
+      </c>
+      <c r="F43" s="19">
+        <v>3</v>
+      </c>
+      <c r="G43" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.5">
-      <c r="A44" s="1">
+    <row r="44" spans="1:7">
+      <c r="A44" s="19">
         <v>113</v>
       </c>
-      <c r="B44" s="1">
-        <v>3</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="B44" s="19">
+        <v>3</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="1">
-        <v>4</v>
-      </c>
-      <c r="F44" s="1">
-        <v>4</v>
-      </c>
-      <c r="G44" s="1">
+      <c r="D44" s="19">
+        <v>4</v>
+      </c>
+      <c r="F44" s="19">
+        <v>4</v>
+      </c>
+      <c r="G44" s="19">
         <v>18000</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.5">
-      <c r="A45" s="1">
+    <row r="45" spans="1:7">
+      <c r="A45" s="19">
         <v>114</v>
       </c>
-      <c r="B45" s="1">
-        <v>4</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="B45" s="19">
+        <v>4</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1"/>
     <row r="47" spans="1:7" ht="15" thickBot="1">
-      <c r="D47" s="10" t="s">
+      <c r="A47" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="14"/>
-      <c r="F47" s="13"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="16"/>
     </row>
     <row r="48" spans="1:7" ht="16" customHeight="1">
-      <c r="D48" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="16" t="s">
+      <c r="A48" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.5">
-      <c r="D49" s="1">
+    <row r="49" spans="1:7">
+      <c r="A49" s="19">
         <v>111</v>
       </c>
-      <c r="E49" s="1">
+      <c r="B49" s="19">
         <v>10</v>
       </c>
-      <c r="F49" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="16.5">
-      <c r="D50" s="1">
+      <c r="C49" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="19">
         <v>112</v>
       </c>
-      <c r="E50" s="1">
+      <c r="B50" s="19">
         <v>10</v>
       </c>
-      <c r="F50" s="1">
+      <c r="C50" s="19">
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.5">
-      <c r="D51" s="1">
+    <row r="51" spans="1:7">
+      <c r="A51" s="19">
         <v>113</v>
       </c>
-      <c r="E51" s="1">
+      <c r="B51" s="19">
         <v>11</v>
       </c>
-      <c r="F51" s="1">
+      <c r="C51" s="19">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.5">
-      <c r="D52" s="1">
+    <row r="52" spans="1:7">
+      <c r="A52" s="19">
         <v>114</v>
       </c>
-      <c r="E52" s="1">
+      <c r="B52" s="19">
         <v>15</v>
       </c>
-      <c r="F52" s="1">
+      <c r="C52" s="19">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.5">
-      <c r="D53" s="1">
+    <row r="53" spans="1:7">
+      <c r="A53" s="19">
         <v>111</v>
       </c>
-      <c r="E53" s="1">
+      <c r="B53" s="19">
         <v>15</v>
       </c>
-      <c r="F53" s="1">
+      <c r="C53" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" customHeight="1" thickBot="1"/>
     <row r="55" spans="1:7" ht="20" customHeight="1">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="9"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="5"/>
     </row>
     <row r="57" spans="1:7" ht="18" customHeight="1">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="15" t="s">
+      <c r="D57" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.5">
-      <c r="A58" s="1">
-        <v>1</v>
-      </c>
-      <c r="B58" s="1">
-        <v>1</v>
-      </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="1">
+    <row r="58" spans="1:7">
+      <c r="A58" s="19">
+        <v>1</v>
+      </c>
+      <c r="B58" s="19">
+        <v>1</v>
+      </c>
+      <c r="C58" s="19">
+        <v>1</v>
+      </c>
+      <c r="D58" s="19">
         <v>10</v>
       </c>
-      <c r="E58" s="1">
-        <v>3</v>
-      </c>
-      <c r="F58" s="1">
-        <v>3</v>
-      </c>
-      <c r="G58" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="16.5">
-      <c r="A59" s="1">
-        <v>2</v>
-      </c>
-      <c r="B59" s="1">
-        <v>2</v>
-      </c>
-      <c r="C59" s="1">
-        <v>2</v>
-      </c>
-      <c r="D59" s="1">
+      <c r="E58" s="19">
+        <v>3</v>
+      </c>
+      <c r="F58" s="19">
+        <v>3</v>
+      </c>
+      <c r="G58" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="19">
+        <v>2</v>
+      </c>
+      <c r="B59" s="19">
+        <v>2</v>
+      </c>
+      <c r="C59" s="19">
+        <v>2</v>
+      </c>
+      <c r="D59" s="19">
         <v>10</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="19">
         <v>6</v>
       </c>
-      <c r="F59" s="1">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="16.5">
-      <c r="A60" s="1">
-        <v>3</v>
-      </c>
-      <c r="B60" s="1">
-        <v>3</v>
-      </c>
-      <c r="C60" s="1">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="F59" s="19">
+        <v>1</v>
+      </c>
+      <c r="G59" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="19">
+        <v>3</v>
+      </c>
+      <c r="B60" s="19">
+        <v>3</v>
+      </c>
+      <c r="C60" s="19">
+        <v>3</v>
+      </c>
+      <c r="D60" s="19">
         <v>11</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="19">
         <v>12</v>
       </c>
-      <c r="F60" s="1">
-        <v>4</v>
-      </c>
-      <c r="G60" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="16.5">
-      <c r="A61" s="1">
-        <v>4</v>
-      </c>
-      <c r="B61" s="1">
-        <v>4</v>
-      </c>
-      <c r="C61" s="1">
-        <v>4</v>
-      </c>
-      <c r="D61" s="1">
+      <c r="F60" s="19">
+        <v>4</v>
+      </c>
+      <c r="G60" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="19">
+        <v>4</v>
+      </c>
+      <c r="B61" s="19">
+        <v>4</v>
+      </c>
+      <c r="C61" s="19">
+        <v>4</v>
+      </c>
+      <c r="D61" s="19">
         <v>15</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="19">
         <v>8</v>
       </c>
-      <c r="F61" s="1">
-        <v>4</v>
-      </c>
-      <c r="G61" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="16.5">
-      <c r="A62" s="1">
-        <v>1</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
-      </c>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="1">
+      <c r="F61" s="19">
+        <v>4</v>
+      </c>
+      <c r="G61" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="19">
+        <v>1</v>
+      </c>
+      <c r="B62" s="19">
+        <v>1</v>
+      </c>
+      <c r="C62" s="19">
+        <v>1</v>
+      </c>
+      <c r="D62" s="19">
         <v>15</v>
       </c>
-      <c r="E62" s="1">
-        <v>2</v>
-      </c>
-      <c r="F62" s="1">
-        <v>3</v>
-      </c>
-      <c r="G62" s="1">
+      <c r="E62" s="19">
+        <v>2</v>
+      </c>
+      <c r="F62" s="19">
+        <v>3</v>
+      </c>
+      <c r="G62" s="19">
         <v>1</v>
       </c>
     </row>
@@ -1555,7 +1551,7 @@
   <mergeCells count="10">
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A12:G12"/>
@@ -1565,5 +1561,6 @@
     <mergeCell ref="A38:G38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>